--- a/docs/培训/OpenWorker培训/01-质量周报/检验记录-装配车间.xlsx
+++ b/docs/培训/OpenWorker培训/01-质量周报/检验记录-装配车间.xlsx
@@ -506,11 +506,11 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>P39Z001</t>
+          <t>P40Z001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,11 +552,11 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P39Z002</t>
+          <t>P40Z002</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -598,11 +598,11 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>P39Z003</t>
+          <t>P40Z003</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -644,11 +644,11 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46287</v>
+        <v>46294</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P39Z004</t>
+          <t>P40Z004</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -690,11 +690,11 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46287</v>
+        <v>46294</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>P39Z005</t>
+          <t>P40Z005</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -736,11 +736,11 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46287</v>
+        <v>46294</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P39Z006</t>
+          <t>P40Z006</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -790,11 +790,11 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46288</v>
+        <v>46295</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>P39Z007</t>
+          <t>P40Z007</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -844,11 +844,11 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46288</v>
+        <v>46295</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>P39Z008</t>
+          <t>P40Z008</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -890,11 +890,11 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46288</v>
+        <v>46295</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>P39Z009</t>
+          <t>P40Z009</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -936,11 +936,11 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46289</v>
+        <v>46296</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>P39Z010</t>
+          <t>P40Z010</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -982,11 +982,11 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46289</v>
+        <v>46296</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>P39Z011</t>
+          <t>P40Z011</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1028,11 +1028,11 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46289</v>
+        <v>46296</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>P39Z012</t>
+          <t>P40Z012</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1074,11 +1074,11 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46290</v>
+        <v>46297</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>P39Z013</t>
+          <t>P40Z013</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1120,11 +1120,11 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46290</v>
+        <v>46297</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>P39Z014</t>
+          <t>P40Z014</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1166,11 +1166,11 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46290</v>
+        <v>46297</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>P39Z015</t>
+          <t>P40Z015</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
